--- a/example/reference_results/9_phyloseq_object/SILVA/phyloseq_summary_silva.xlsx
+++ b/example/reference_results/9_phyloseq_object/SILVA/phyloseq_summary_silva.xlsx
@@ -942,25 +942,25 @@
     <t xml:space="preserve">SILVA_raw_counts</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/5_dada2_pipeline/asv_count_table.csv</t>
+    <t xml:space="preserve">example/run_results/5_dada2_pipeline/asv_count_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">0bbe2347056168fb16c7516740207068</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/5_dada2_pipeline/silva_taxonomy_table.csv</t>
+    <t xml:space="preserve">example/run_results/5_dada2_pipeline/silva_taxonomy_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">2b72faf4ba43cde35a0a4b85bf3c25df</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/data/metadata.tsv</t>
+    <t xml:space="preserve">example/data/metadata.tsv</t>
   </si>
   <si>
     <t xml:space="preserve">8a016686bccd6a49787b7859a1de0436</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/6_phylogenetic_tree/phylogenetic_tree.nwk</t>
+    <t xml:space="preserve">example/run_results/6_phylogenetic_tree/phylogenetic_tree.nwk</t>
   </si>
   <si>
     <t xml:space="preserve">2a0c61f68343e387fae4c899fc2608ae</t>
@@ -975,13 +975,13 @@
     <t xml:space="preserve">SILVA_copy_number_corrected</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
+    <t xml:space="preserve">example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c947e7664fb75efd061c5c8de721b7e8</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/7_copy_number_correction/copy_number_correction_summary.xlsx</t>
+    <t xml:space="preserve">example/run_results/7_copy_number_correction/copy_number_correction_summary.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">17f2c4800567a35d794771c3b6a3de3e</t>
@@ -990,16 +990,16 @@
     <t xml:space="preserve">SILVA_microbial_load_corrected</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/8_microbial_load_correction/microbial_load_corrected_abundance_table.csv</t>
+    <t xml:space="preserve">example/run_results/8_microbial_load_correction/microbial_load_corrected_abundance_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">055887ea8e51ec34a9a0f51d6d4df72f</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_Illumina_PairedEnd_Workflow/example/run_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24c77d4ef843e5b9b8c08f073deb4bd1</t>
+    <t xml:space="preserve">example/run_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77eedebb367080654f13a6756ffb1de5</t>
   </si>
   <si>
     <t xml:space="preserve">Sheet</t>
